--- a/data/satisfaction_summary/2026/1-2月/1-2月客户类型满意度汇总表.xlsx
+++ b/data/satisfaction_summary/2026/1-2月/1-2月客户类型满意度汇总表.xlsx
@@ -1034,7 +1034,7 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>酒店会议活动主（承）办</t>
+          <t>酒店会议主（承）办</t>
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
